--- a/data/downloads/sgx1UxHhyd9Q3mC6fqIRhMWz.xlsx
+++ b/data/downloads/sgx1UxHhyd9Q3mC6fqIRhMWz.xlsx
@@ -3502,7 +3502,7 @@
       <c r="A22" s="1" t="inlineStr"/>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>Coverage gaps: there is no NIH research-funding data yet, and Long COVID breakdowns by sex, age and race are not yet computed. MEPS releases a 3-character diagnosis code only when at least 30 sampled people carry it, so the Lyme code (A69) is missing from most recent years, and AHRQ advises against estimating Lyme costs from MEPS.</t>
+          <t>Coverage gaps: there is no NIH research-funding data yet, and Long COVID breakdowns by sex, age and race are not yet computed. MEPS releases a 3-character diagnosis code only when at least 30 sampled people carry it, so the Lyme code (A69) is missing from most recent years. In a written answer to the sprint, an AHRQ data steward said the pooled sample is too small for good Lyme cost estimates and urged caution.</t>
         </is>
       </c>
     </row>

--- a/data/downloads/sgx1UxHhyd9Q3mC6fqIRhMWz.xlsx
+++ b/data/downloads/sgx1UxHhyd9Q3mC6fqIRhMWz.xlsx
@@ -702,7 +702,7 @@
       <c r="A32" s="1" t="inlineStr"/>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>This does not replace your care team: it is a decision-support model for interpreting this document's own evidence, not a diagnosis or an individual treatment plan.</t>
+          <t>This does not replace your care team: it is a what-if model for interpreting this document's own evidence, not a diagnosis or an individual treatment plan.</t>
         </is>
       </c>
     </row>
